--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/통합 클라우드 버전(HP^M시설관리)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B78FE0-4442-465F-AF25-6BD46BDB3525}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF21B70-5CDC-4C5B-BD9B-34BAFA0BCDB0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="177">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1481,6 +1481,14 @@
       </rPr>
       <t xml:space="preserve">사업소득자 신고"  계좌이체 함 (개인) </t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">태양광 설치 검토 </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1751,10 +1759,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3103,11 +3107,21 @@
       </c>
     </row>
     <row r="26" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="A26" s="4">
+        <v>23</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46240</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF21B70-5CDC-4C5B-BD9B-34BAFA0BCDB0}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05EF9E50-AD79-4F51-BDCA-CF03C32989D2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="183">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1230,6 +1230,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1390,6 +1391,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1409,6 +1411,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1484,11 +1487,65 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>옥상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">태양광 설치 검토 </t>
+    <t>1층 재단기</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재단기</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-10</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>소모품보충</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미세한 잡소리 발생 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기어오일부족 --&gt; 보충</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">기어오일 보충(오말라 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>G460)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기어오일 2리터 추가 구매 _ 보충"</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1759,6 +1816,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -1970,7 +2031,7 @@
     <col min="8" max="8" width="28.5703125" style="20" customWidth="1"/>
     <col min="9" max="9" width="29" style="20" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" style="20" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" style="20" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" style="20" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="21" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" style="20" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" style="20" customWidth="1"/>
@@ -3111,10 +3172,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="7">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>175</v>
@@ -3122,17 +3183,39 @@
       <c r="E26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="1"/>
+      <c r="F26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="L26" s="6">
+        <v>18000</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="27" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05EF9E50-AD79-4F51-BDCA-CF03C32989D2}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF484C2-0326-4C36-BD9D-ECE5F2B60580}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1495,10 +1495,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>TO-10</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>소모품보충</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1546,6 +1542,10 @@
       </rPr>
       <t>기어오일 2리터 추가 구매 _ 보충"</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-11</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2031,7 +2031,7 @@
     <col min="8" max="8" width="28.5703125" style="20" customWidth="1"/>
     <col min="9" max="9" width="29" style="20" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" style="20" customWidth="1"/>
-    <col min="11" max="11" width="26.7109375" style="20" customWidth="1"/>
+    <col min="11" max="11" width="30.28515625" style="20" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="21" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" style="20" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" style="20" customWidth="1"/>
@@ -3184,22 +3184,22 @@
         <v>176</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K26" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="L26" s="6">
         <v>18000</v>
@@ -3214,7 +3214,7 @@
         <v>24</v>
       </c>
       <c r="P26" s="27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF484C2-0326-4C36-BD9D-ECE5F2B60580}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F9C2502-1408-4CE9-A046-044DC1DC7BE7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,62 +39,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="239">
   <si>
     <t xml:space="preserve">일자 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>대상설비명</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>관리번호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>구분</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>발생현상(문제점)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>원인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>조치내용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>교체부품명</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>소요비용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>수행업체</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>작업자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">비고 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>NO</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>구역</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -110,19 +110,19 @@
       </rPr>
       <t>층 남자화장실</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>진행상태</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BO-B01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">고장수리 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -138,15 +138,15 @@
       </rPr>
       <t>감암밸브 누수 현상 발생</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>고무패킹 마모</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부품 교체</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -168,19 +168,19 @@
       </rPr>
       <t>A</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>자체처리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">김기태 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">완료 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -211,11 +211,11 @@
       </rPr>
       <t xml:space="preserve">도어클로저 </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ME-B01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -231,11 +231,11 @@
       </rPr>
       <t>도어클로저 유압 누수 발생</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">유압 누수 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -261,7 +261,7 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -300,7 +300,7 @@
       </rPr>
       <t>유지보수 수리 이력 *</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -336,19 +336,19 @@
       </rPr>
       <t>남자화장실</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>세면대 수전</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> TO-S01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>고장교체</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -364,7 +364,7 @@
       </rPr>
       <t>부분 누수 발생</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -380,7 +380,7 @@
       </rPr>
       <t>세면대 수전</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -402,7 +402,7 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -438,35 +438,35 @@
       </rPr>
       <t>현장내</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">톰슨3호기 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부품교체</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>구분</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>설비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>장비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PR-T01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">온수보일러 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -482,11 +482,11 @@
       </rPr>
       <t xml:space="preserve">불이 안 들어옴 </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부품 고장</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -508,7 +508,7 @@
       </rPr>
       <t>LED T5</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -544,15 +544,15 @@
       </rPr>
       <t>현장내</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>핸드자키</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PR-H01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -568,19 +568,19 @@
       </rPr>
       <t>고장수리</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>도어클로저 유압 부족</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>유압 부분 누수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>고장수리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -596,11 +596,11 @@
       </rPr>
       <t>리터</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>시설</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -616,31 +616,31 @@
       </rPr>
       <t>층 현관문</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>바닥 대리석</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HR-H01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부분보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>대리석 파손</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>외부충격(지게차)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>몰탈, 돌접착제 보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -656,15 +656,15 @@
       </rPr>
       <t xml:space="preserve">욕조 부레 </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-S02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>압력조절밸브 이상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -696,19 +696,19 @@
       </rPr>
       <t>마모</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">욕조 부레 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>설비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -724,11 +724,11 @@
       </rPr>
       <t>층 설비실</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-S03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -744,15 +744,15 @@
       </rPr>
       <t>부품교체</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>세면대 밸브(고무경화)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>밸브 경화로 인한 누수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -784,75 +784,75 @@
       </rPr>
       <t>교체</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>밸브 셋트</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>화성종합밸브(031-557-1716)_도농역근처</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>옥외주차장수전</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>옥외주차장</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-S04</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>수전밸브 조절 불가</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>수전밸브 고장</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>수전밸브 셋트</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>외주업체</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이봉수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>옥상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HR-04</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>옥상방수 (소회의실)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">옥상방수 누수발생 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">부분 크렉 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">방수제 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -868,27 +868,27 @@
       </rPr>
       <t>층 출입구(목형창구옆)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>출입구 레일 불량</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-05</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>레일 베어링 마모</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>여 닫을떄 원활하지 않음</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부품교체예정</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -904,23 +904,23 @@
       </rPr>
       <t xml:space="preserve">층 여자 화장실 </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>좌측 좌변기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-06</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부분보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>좌변수전 누수 현상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -952,19 +952,19 @@
       </rPr>
       <t>마모 및 경화</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>고무패킹 보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부품교체요망</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>임시조치</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -980,7 +980,7 @@
       </rPr>
       <t xml:space="preserve"> 처리</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1046,74 +1046,74 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>바닥 타일</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HR-08</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">타일 깨짐 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>외부충격</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>타일보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>설비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>주차장 부동전 수리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>옥상 바닥</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>옥상 방수 누수 발생</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">바닥 누수 발생 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>바닥 방수제 보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-08</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-09</t>
   </si>
   <si>
     <t>보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이봉수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>추가보완예정</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>장비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1129,43 +1129,43 @@
       </rPr>
       <t>원격 프로그램</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PR-H14</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>복구</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>데이터 복구 진행</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>프로그램 재 설치</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">재 설치 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">프로그램 버그 발생 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>데이터 연동 이상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>재 설치</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>GHP 원격 프로그램</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1201,15 +1201,15 @@
       </rPr>
       <t>프로그램</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이사님실 (GHP 컴퓨터 본체)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>15번 처리 완료(옥상 빔 주위 보수 작업(근본적인 원인이었음)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1245,7 +1245,7 @@
       </rPr>
       <t>현장내</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1277,35 +1277,35 @@
       </rPr>
       <t>문 고정(목형창고쪽)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>시설</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HR-11</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">문고정 불량 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">고정 경첩 마모 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">보수 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">피스 변경 보수 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>267/24</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1321,39 +1321,39 @@
       </rPr>
       <t>층 현장내</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">대형출입문 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HR-12</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부분보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>고정 레일 베어링 흔들림</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>잦은 사용으로 인한 마모</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>보수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>고정 베어링</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이봉수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1369,11 +1369,11 @@
       </rPr>
       <t xml:space="preserve">층 옵셋2호기 전기실 입구 </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HR-14</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1416,19 +1416,19 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">전기실 칸막이 설치 진행 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">칸막이 작업 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>설비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1444,31 +1444,31 @@
       </rPr>
       <t>층 휴게실</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>벽걸이 에어컨</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-10</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">시원하지 않음 --&gt; 냉매보충 및 콘덴서 교체 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>콘덴서 불량 , 냉매부족</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>콘덴서</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이봉수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1484,27 +1484,27 @@
       </rPr>
       <t xml:space="preserve">사업소득자 신고"  계좌이체 함 (개인) </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>1층 재단기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>재단기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>소모품보충</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">미세한 잡소리 발생 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>기어오일부족 --&gt; 보충</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1526,7 +1526,7 @@
       </rPr>
       <t>G460)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1542,11 +1542,852 @@
       </rPr>
       <t>기어오일 2리터 추가 구매 _ 보충"</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TO-11</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방 실외기 #2번</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-14</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>난방 간헐적 이상</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">압축기이상 --&gt; 교체 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>압축기 교체진행 (2대)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무상 A/S (2번실외기) </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실외기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> #2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉매부족 , 냉동오일 --&gt;보충 및 교체</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품보충 및 교체 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉매충진, 냉동오일 교체</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> A/S (2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번실외기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실외기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> #2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>리턴파이프 교체, 냉매 보충</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>리턴파이트, 냉매보충</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥상 실외기(GHP)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실외기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> #6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-15</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>난방</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간헐적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> A/S (6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번 실외기)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방 실외기 #5번</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-16</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에러 코드 발생</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔진오일 교체 및 보충 시기 도래</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>오일 보충, 오일필터, 점화플러그 교체</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>유상처리 (5번 실외기엔진오일 1회 - 1만시간 도래)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방 실외기 #4번</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-17</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>압축기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교체진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무상 A/S(4번 실외기) </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방 실외기 #5번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>압축기 교체진행(2대)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(5번 실외기)</t>
+  </si>
+  <si>
+    <t>압축기 필터 이상 --&gt; 교체</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>압축기 필터 교체 (2대)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(6번 실외기)</t>
+  </si>
+  <si>
+    <t>무상 A/S(5번 실외기)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>압축기 교체진행(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(4번 실외기)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>옥상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실외기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>(GHP)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방 실외기 #3번</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-18</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>압축기 선제 대응 교체(2대)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(3번 실외기)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방 실외기 #1번</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-19</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>압축기 선</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(1번 실외기)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방 실외기 #2번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">LB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에러 코드 발생</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GHP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉난방 실외기 #3번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>예정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>`39</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(20,882</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간(2회째))</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(10,406</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간(1회쨰)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1557,11 +2398,19 @@
     <numFmt numFmtId="176" formatCode="&quot;₩&quot;#,##0"/>
     <numFmt numFmtId="177" formatCode="yy&quot;/&quot;m&quot;/&quot;d;@"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1661,7 +2510,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1683,6 +2532,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1714,23 +2569,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1739,40 +2594,40 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1781,23 +2636,35 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2029,14 +2896,14 @@
     <col min="6" max="6" width="14.42578125" style="20" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="20" customWidth="1"/>
     <col min="8" max="8" width="28.5703125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="29" style="20" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" customWidth="1"/>
-    <col min="11" max="11" width="30.28515625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="37.5703125" style="20" customWidth="1"/>
+    <col min="10" max="10" width="21" style="20" customWidth="1"/>
+    <col min="11" max="11" width="36.7109375" style="20" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="21" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" style="20" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" style="20" customWidth="1"/>
     <col min="15" max="15" width="14.28515625" style="20" customWidth="1"/>
-    <col min="16" max="16" width="51" customWidth="1"/>
+    <col min="16" max="16" width="73.85546875" customWidth="1"/>
     <col min="17" max="29" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3218,292 +4085,804 @@
       </c>
     </row>
     <row r="27" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="1"/>
+      <c r="A27" s="4">
+        <v>24</v>
+      </c>
+      <c r="B27" s="7">
+        <v>44552</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L27" s="6">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P27" s="15" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="1"/>
+      <c r="A28" s="4">
+        <v>25</v>
+      </c>
+      <c r="B28" s="7">
+        <v>44553</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L28" s="6">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P28" s="28" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="1"/>
+      <c r="A29" s="4">
+        <v>26</v>
+      </c>
+      <c r="B29" s="7">
+        <v>44566</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="L29" s="6">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" s="28" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="1"/>
+      <c r="A30" s="4">
+        <v>27</v>
+      </c>
+      <c r="B30" s="7">
+        <v>44650</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L30" s="6">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P30" s="28" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="1"/>
+      <c r="A31" s="4">
+        <v>28</v>
+      </c>
+      <c r="B31" s="7">
+        <v>44830</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L31" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P31" s="29" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="1"/>
+      <c r="A32" s="4">
+        <v>29</v>
+      </c>
+      <c r="B32" s="7">
+        <v>44903</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P32" s="15" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="33" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="1"/>
+      <c r="A33" s="4">
+        <v>30</v>
+      </c>
+      <c r="B33" s="7">
+        <v>44931</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L33" s="6">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P33" s="15" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="1"/>
+      <c r="A34" s="4">
+        <v>31</v>
+      </c>
+      <c r="B34" s="7">
+        <v>44930</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P34" s="15" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="35" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="1"/>
+      <c r="A35" s="4">
+        <v>32</v>
+      </c>
+      <c r="B35" s="7">
+        <v>44935</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P35" s="15" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="36" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="1"/>
+      <c r="A36" s="4">
+        <v>33</v>
+      </c>
+      <c r="B36" s="7">
+        <v>44937</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P36" s="15" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="37" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="1"/>
+      <c r="A37" s="4">
+        <v>34</v>
+      </c>
+      <c r="B37" s="7">
+        <v>44938</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P37" s="15" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="38" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="1"/>
+      <c r="A38" s="4">
+        <v>35</v>
+      </c>
+      <c r="B38" s="7">
+        <v>44938</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="L38" s="6">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P38" s="15" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="39" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="1"/>
+      <c r="A39" s="4">
+        <v>36</v>
+      </c>
+      <c r="B39" s="7">
+        <v>45740</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L39" s="6">
+        <v>400000</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P39" s="30" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="40" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="1"/>
+      <c r="A40" s="4">
+        <v>37</v>
+      </c>
+      <c r="B40" s="7">
+        <v>45827</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L40" s="6">
+        <v>400000</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P40" s="30" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="41" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="1"/>
+      <c r="A41" s="4">
+        <v>38</v>
+      </c>
+      <c r="B41" s="7">
+        <v>46244</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L41" s="6">
+        <v>400000</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O41" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="P41" s="30" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="42" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="1"/>
+      <c r="A42" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46244</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L42" s="6">
+        <v>400000</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O42" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="P42" s="30" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="43" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
@@ -4702,7 +6081,7 @@
     <row r="999" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:P13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F9C2502-1408-4CE9-A046-044DC1DC7BE7}"/>
+  <xr:revisionPtr revIDLastSave="448" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D14AC404-C8FD-4523-AC89-5E88811A288D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="248">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2304,10 +2304,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>`39</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve"> 5</t>
     </r>
@@ -2386,6 +2382,81 @@
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 식당내 의자</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">층 식당내 의자 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+  </si>
+  <si>
+    <t>벤치형의자 판 이탈</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤치형의자 판 이탈 --&gt; 홀가공 작업 진행</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>홀가공 작업 진행(케이블타이로 고정함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">벤치형 의자 보수 수량 총 6대 ---&gt; 지속적인 관찰 필요 함 </t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2896,9 +2967,9 @@
     <col min="6" max="6" width="14.42578125" style="20" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="20" customWidth="1"/>
     <col min="8" max="8" width="28.5703125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="37.5703125" style="20" customWidth="1"/>
+    <col min="9" max="9" width="42" style="20" customWidth="1"/>
     <col min="10" max="10" width="21" style="20" customWidth="1"/>
-    <col min="11" max="11" width="36.7109375" style="20" customWidth="1"/>
+    <col min="11" max="11" width="41.7109375" style="20" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="21" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" style="20" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" style="20" customWidth="1"/>
@@ -4831,12 +4902,12 @@
         <v>235</v>
       </c>
       <c r="P41" s="30" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>236</v>
+      <c r="A42" s="2">
+        <v>39</v>
       </c>
       <c r="B42" s="7">
         <v>46244</v>
@@ -4881,26 +4952,58 @@
         <v>235</v>
       </c>
       <c r="P42" s="30" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="1"/>
+      <c r="A43" s="4">
+        <v>40</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46244</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G43" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="L43" s="6">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P43" s="27" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="44" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="448" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D14AC404-C8FD-4523-AC89-5E88811A288D}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51B848FD-597E-4B6C-9A84-22ADC5E38444}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="257">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2422,10 +2422,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>TO20</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>부분보수</t>
   </si>
   <si>
@@ -2457,6 +2453,98 @@
         <charset val="129"/>
       </rPr>
       <t xml:space="preserve">벤치형 의자 보수 수량 총 6대 ---&gt; 지속적인 관찰 필요 함 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 여자휴게실</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선풍기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-21</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">작동 안됨 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이탈 및 먼지 쌓임 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 분해 청소 및 부품 재조립</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회전축 이상으로 고정형으로만  사용 가능 함</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -4143,7 +4231,7 @@
         <v>18000</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>23</v>
@@ -4972,22 +5060,22 @@
         <v>240</v>
       </c>
       <c r="F43" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G43" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="G43" s="25" t="s">
+      <c r="H43" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="I43" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="L43" s="6">
         <v>0</v>
@@ -5002,26 +5090,58 @@
         <v>24</v>
       </c>
       <c r="P43" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="1"/>
+      <c r="A44" s="4">
+        <v>41</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46244</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="L44" s="6">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P44" s="27" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="45" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="467" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51B848FD-597E-4B6C-9A84-22ADC5E38444}"/>
+  <xr:revisionPtr revIDLastSave="487" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD9893D-DC8C-4B72-9581-ECFCF1C479AF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="266">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2545,6 +2545,97 @@
         <charset val="129"/>
       </rPr>
       <t>회전축 이상으로 고정형으로만  사용 가능 함</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">층 1호 접착기 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">형광등 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-22</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부픔교체</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전등 계속 깜박임 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">안정기 불량 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>아쎄이 전부 교체(2층 창고쪽과 맞교체 함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">형광등의 내구연수는 7년 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>~10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 (현 제품 단종) --&gt; 기존 정상제품(2층 창고문앞쪽)과 맞교체 진행 함</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -3057,12 +3148,12 @@
     <col min="8" max="8" width="28.5703125" style="20" customWidth="1"/>
     <col min="9" max="9" width="42" style="20" customWidth="1"/>
     <col min="10" max="10" width="21" style="20" customWidth="1"/>
-    <col min="11" max="11" width="41.7109375" style="20" customWidth="1"/>
+    <col min="11" max="11" width="44.28515625" style="20" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="21" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" style="20" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" style="20" customWidth="1"/>
     <col min="15" max="15" width="14.28515625" style="20" customWidth="1"/>
-    <col min="16" max="16" width="73.85546875" customWidth="1"/>
+    <col min="16" max="16" width="87.85546875" customWidth="1"/>
     <col min="17" max="29" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5144,22 +5235,54 @@
       </c>
     </row>
     <row r="45" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="1"/>
+      <c r="A45" s="4">
+        <v>42</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46246</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="L45" s="6">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O45" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P45" s="27" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="46" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="487" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD9893D-DC8C-4B72-9581-ECFCF1C479AF}"/>
+  <xr:revisionPtr revIDLastSave="504" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00E48963-842B-4E29-BD85-FC8963625CEF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="274">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2637,6 +2637,50 @@
       </rPr>
       <t>년 (현 제품 단종) --&gt; 기존 정상제품(2층 창고문앞쪽)과 맞교체 진행 함</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 시야기</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>반자동 핸드자키</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO24</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상.하 작동 레버 파손</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>외부 충격에 의한 작동 레버 파손</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">프라스틱으로 규격에 맞게 가공 장착함 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>임시조치 한 상태임,  추후 가공제품 소손시  부품 교체 예정 임</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2933,10 +2977,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -5285,22 +5325,54 @@
       </c>
     </row>
     <row r="46" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="1"/>
+      <c r="A46" s="4">
+        <v>43</v>
+      </c>
+      <c r="B46" s="7">
+        <v>46260</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="L46" s="6">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O46" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="P46" s="15" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="47" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="504" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00E48963-842B-4E29-BD85-FC8963625CEF}"/>
+  <xr:revisionPtr revIDLastSave="509" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B50AAA06-8D00-4D67-9E30-8645AA7EBB51}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="273">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2300,7 +2300,301 @@
     </r>
   </si>
   <si>
-    <t>예정</t>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 식당내 의자</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">층 식당내 의자 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+  </si>
+  <si>
+    <t>벤치형의자 판 이탈</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤치형의자 판 이탈 --&gt; 홀가공 작업 진행</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>홀가공 작업 진행(케이블타이로 고정함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">벤치형 의자 보수 수량 총 6대 ---&gt; 지속적인 관찰 필요 함 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 여자휴게실</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선풍기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-21</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">작동 안됨 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이탈 및 먼지 쌓임 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 분해 청소 및 부품 재조립</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회전축 이상으로 고정형으로만  사용 가능 함</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">층 1호 접착기 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">형광등 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-22</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부픔교체</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전등 계속 깜박임 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">안정기 불량 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>아쎄이 전부 교체(2층 창고쪽과 맞교체 함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">형광등의 내구연수는 7년 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>~10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 (현 제품 단종) --&gt; 기존 정상제품(2층 창고문앞쪽)과 맞교체 진행 함</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 시야기</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>반자동 핸드자키</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO24</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상.하 작동 레버 파손</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>외부 충격에 의한 작동 레버 파손</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">프라스틱으로 규격에 맞게 가공 장착함 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>임시조치 한 상태임,  추후 가공제품 소손시  부품 교체 예정 임</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -2337,22 +2631,6 @@
       </rPr>
       <t>시간(2회째))</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
-    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2361,7 +2639,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(10,406</t>
+      <t>_#5</t>
     </r>
     <r>
       <rPr>
@@ -2371,7 +2649,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>시간(1회쨰)</t>
+      <t>번</t>
     </r>
     <r>
       <rPr>
@@ -2381,306 +2659,74 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>층 식당내 의자</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">층 식당내 의자 </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>부분보수</t>
-  </si>
-  <si>
-    <t>벤치형의자 판 이탈</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>벤치형의자 판 이탈 --&gt; 홀가공 작업 진행</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>부분보수</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>홀가공 작업 진행(케이블타이로 고정함)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">벤치형 의자 보수 수량 총 6대 ---&gt; 지속적인 관찰 필요 함 </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>층 여자휴게실</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>선풍기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO-20</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO-21</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>부분보수</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">작동 안됨 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부품</t>
+      <t>(260827)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">이탈 및 먼지 쌓임 </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체 분해 청소 및 부품 재조립</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회전축 이상으로 고정형으로만  사용 가능 함</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">층 1호 접착기 </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">LED </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">형광등 </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO-22</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>부픔교체</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">전등 계속 깜박임 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">안정기 불량 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>아쎄이 전부 교체(2층 창고쪽과 맞교체 함)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> LED </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">형광등의 내구연수는 7년 </t>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(10,406</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간(1회쨰)</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
-        <family val="3"/>
-      </rPr>
-      <t>~10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>년 (현 제품 단종) --&gt; 기존 정상제품(2층 창고문앞쪽)과 맞교체 진행 함</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>층 시야기</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>반자동 핸드자키</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO24</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>상.하 작동 레버 파손</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>외부 충격에 의한 작동 레버 파손</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">프라스틱으로 규격에 맞게 가공 장착함 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>임시조치 한 상태임,  추후 가공제품 소손시  부품 교체 예정 임</t>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)_#4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(260827)</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2863,7 +2909,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2957,9 +3003,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2975,6 +3018,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5117,11 +5164,11 @@
       <c r="N41" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="O41" s="31" t="s">
-        <v>235</v>
+      <c r="O41" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="P41" s="30" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5167,11 +5214,11 @@
       <c r="N42" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="O42" s="31" t="s">
-        <v>235</v>
+      <c r="O42" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="P42" s="30" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5182,31 +5229,31 @@
         <v>46244</v>
       </c>
       <c r="C43" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G43" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="H43" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="I43" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G43" s="25" t="s">
+      <c r="J43" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="L43" s="6">
         <v>0</v>
@@ -5221,7 +5268,7 @@
         <v>24</v>
       </c>
       <c r="P43" s="27" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5232,31 +5279,31 @@
         <v>46244</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="G44" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="H44" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>254</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="L44" s="6">
         <v>0</v>
@@ -5271,7 +5318,7 @@
         <v>24</v>
       </c>
       <c r="P44" s="27" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5282,31 +5329,31 @@
         <v>46246</v>
       </c>
       <c r="C45" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="G45" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="H45" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="I45" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>78</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L45" s="6">
         <v>0</v>
@@ -5321,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="P45" s="27" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5332,31 +5379,31 @@
         <v>46260</v>
       </c>
       <c r="C46" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>62</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L46" s="6">
         <v>0</v>
@@ -5371,7 +5418,7 @@
         <v>110</v>
       </c>
       <c r="P46" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="509" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B50AAA06-8D00-4D67-9E30-8645AA7EBB51}"/>
+  <xr:revisionPtr revIDLastSave="515" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{513AA25F-D07A-4A24-9990-C42F160000C1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="274">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -1872,38 +1872,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>무상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> A/S (6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>번 실외기)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">GHP </t>
     </r>
     <r>
@@ -2184,10 +2152,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>무상 A/S(3번 실외기)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">GHP </t>
     </r>
@@ -2209,10 +2173,6 @@
   </si>
   <si>
     <t>압축기 선</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>무상 A/S(1번 실외기)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -2619,7 +2579,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(20,882</t>
+      <t>(10,715</t>
     </r>
     <r>
       <rPr>
@@ -2629,7 +2589,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>시간(2회째))</t>
+      <t>시간(1회쨰)</t>
     </r>
     <r>
       <rPr>
@@ -2639,7 +2599,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>_#5</t>
+      <t>)_#4</t>
     </r>
     <r>
       <rPr>
@@ -2685,7 +2645,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(10,406</t>
+      <t>(21,327</t>
     </r>
     <r>
       <rPr>
@@ -2695,7 +2655,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>시간(1회쨰)</t>
+      <t>시간(2회째))</t>
     </r>
     <r>
       <rPr>
@@ -2705,7 +2665,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>)_#4</t>
+      <t>_#5</t>
     </r>
     <r>
       <rPr>
@@ -2726,6 +2686,102 @@
         <scheme val="minor"/>
       </rPr>
       <t>(260827)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(1번 실외기)/  #1번: 12,979(26.8.27기준)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  (#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번: 13,587(26.8.27기준))</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(3번 실외기)  (#3번: 15,051(26.8.27기준))</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> A/S (6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번 실외기)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">  (#6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번: 12,345(26.8.27기준))</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -4618,7 +4674,7 @@
         <v>24</v>
       </c>
       <c r="P30" s="28" t="s">
-        <v>202</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4635,25 +4691,25 @@
         <v>198</v>
       </c>
       <c r="E31" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H31" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>177</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L31" s="6">
         <v>1000000</v>
@@ -4668,7 +4724,7 @@
         <v>24</v>
       </c>
       <c r="P31" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4685,10 +4741,10 @@
         <v>198</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>41</v>
@@ -4703,7 +4759,7 @@
         <v>20</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L32" s="6">
         <v>0</v>
@@ -4718,7 +4774,7 @@
         <v>24</v>
       </c>
       <c r="P32" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4735,10 +4791,10 @@
         <v>198</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>41</v>
@@ -4753,7 +4809,7 @@
         <v>20</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L33" s="6">
         <v>0</v>
@@ -4768,7 +4824,7 @@
         <v>24</v>
       </c>
       <c r="P33" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4785,10 +4841,10 @@
         <v>198</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>41</v>
@@ -4797,13 +4853,13 @@
         <v>186</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L34" s="6">
         <v>0</v>
@@ -4818,7 +4874,7 @@
         <v>24</v>
       </c>
       <c r="P34" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4835,10 +4891,10 @@
         <v>198</v>
       </c>
       <c r="E35" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>41</v>
@@ -4853,7 +4909,7 @@
         <v>20</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L35" s="6">
         <v>0</v>
@@ -4868,7 +4924,7 @@
         <v>24</v>
       </c>
       <c r="P35" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4885,10 +4941,10 @@
         <v>198</v>
       </c>
       <c r="E36" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>41</v>
@@ -4903,7 +4959,7 @@
         <v>20</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L36" s="6">
         <v>0</v>
@@ -4918,7 +4974,7 @@
         <v>24</v>
       </c>
       <c r="P36" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4932,13 +4988,13 @@
         <v>183</v>
       </c>
       <c r="D37" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>41</v>
@@ -4953,7 +5009,7 @@
         <v>20</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L37" s="6">
         <v>0</v>
@@ -4968,7 +5024,7 @@
         <v>24</v>
       </c>
       <c r="P37" s="15" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4982,13 +5038,13 @@
         <v>183</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>41</v>
@@ -5003,7 +5059,7 @@
         <v>20</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L38" s="6">
         <v>0</v>
@@ -5018,7 +5074,7 @@
         <v>24</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>230</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5035,7 +5091,7 @@
         <v>198</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>185</v>
@@ -5044,16 +5100,16 @@
         <v>177</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>177</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L39" s="6">
         <v>400000</v>
@@ -5068,7 +5124,7 @@
         <v>24</v>
       </c>
       <c r="P39" s="30" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5085,25 +5141,25 @@
         <v>198</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>177</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L40" s="6">
         <v>400000</v>
@@ -5118,7 +5174,7 @@
         <v>24</v>
       </c>
       <c r="P40" s="30" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5135,25 +5191,25 @@
         <v>198</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H41" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>177</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L41" s="6">
         <v>400000</v>
@@ -5168,7 +5224,7 @@
         <v>24</v>
       </c>
       <c r="P41" s="30" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5185,25 +5241,25 @@
         <v>198</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H42" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>177</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L42" s="6">
         <v>400000</v>
@@ -5218,7 +5274,7 @@
         <v>24</v>
       </c>
       <c r="P42" s="30" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5229,31 +5285,31 @@
         <v>46244</v>
       </c>
       <c r="C43" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G43" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="H43" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="I43" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G43" s="25" t="s">
+      <c r="J43" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="L43" s="6">
         <v>0</v>
@@ -5268,7 +5324,7 @@
         <v>24</v>
       </c>
       <c r="P43" s="27" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5279,31 +5335,31 @@
         <v>46244</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="G44" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="H44" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>251</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="L44" s="6">
         <v>0</v>
@@ -5318,7 +5374,7 @@
         <v>24</v>
       </c>
       <c r="P44" s="27" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5329,31 +5385,31 @@
         <v>46246</v>
       </c>
       <c r="C45" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="G45" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="H45" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="I45" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>78</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L45" s="6">
         <v>0</v>
@@ -5368,7 +5424,7 @@
         <v>24</v>
       </c>
       <c r="P45" s="27" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5379,31 +5435,31 @@
         <v>46260</v>
       </c>
       <c r="C46" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>62</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L46" s="6">
         <v>0</v>
@@ -5418,7 +5474,7 @@
         <v>110</v>
       </c>
       <c r="P46" s="15" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="515" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{513AA25F-D07A-4A24-9990-C42F160000C1}"/>
+  <xr:revisionPtr revIDLastSave="522" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{741B5F8D-5536-4FA6-8CBB-04B3FA65F560}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="sa" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,11 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="274">
-  <si>
-    <t xml:space="preserve">일자 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="275">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2783,6 +2779,14 @@
       </rPr>
       <t>번: 12,345(26.8.27기준))</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">접수일자 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리완료일자</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3279,2209 +3283,2261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P999"/>
+  <dimension ref="A1:Q999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="20" customWidth="1"/>
-    <col min="2" max="3" width="12.85546875" style="18" customWidth="1"/>
-    <col min="4" max="4" width="33" style="20" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="20" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="42" style="20" customWidth="1"/>
-    <col min="10" max="10" width="21" style="20" customWidth="1"/>
-    <col min="11" max="11" width="44.28515625" style="20" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="21" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" style="20" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" style="20" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="20" customWidth="1"/>
-    <col min="16" max="16" width="87.85546875" customWidth="1"/>
-    <col min="17" max="29" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="18" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="33" style="20" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="28.5703125" style="20" customWidth="1"/>
+    <col min="10" max="10" width="42" style="20" customWidth="1"/>
+    <col min="11" max="11" width="21" style="20" customWidth="1"/>
+    <col min="12" max="12" width="44.28515625" style="20" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="21" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" style="20" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" style="20" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="20" customWidth="1"/>
+    <col min="17" max="17" width="87.85546875" customWidth="1"/>
+    <col min="18" max="30" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="19"/>
+        <v>30</v>
+      </c>
+      <c r="E1" s="19"/>
     </row>
-    <row r="2" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="M3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="N3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="P3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="4" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="7">
         <v>46056</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="L4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="M4" s="6">
+        <v>7500</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="6">
-        <v>7500</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="7">
         <v>46064</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="7">
         <v>46058</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="6">
+        <v>8000</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="6">
-        <v>8000</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6" s="4"/>
+      <c r="P6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="7">
         <v>46063</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="M7" s="6">
         <v>4750</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="N7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="P7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="7">
         <v>46073</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="L8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="M8" s="6">
         <v>14500</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="P8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="7">
         <v>46091</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="K9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="M9" s="6">
         <v>26500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="4"/>
+      <c r="N9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
       <c r="B10" s="7">
         <v>46093</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
+      <c r="C10" s="7"/>
+      <c r="D10" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="H10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="J10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="K10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L10" s="6">
+        <v>19</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M10" s="6">
         <v>9000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P10" s="4"/>
+      <c r="N10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
       <c r="B11" s="7">
         <v>46114</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="K11" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="L11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="M11" s="6">
+        <v>3500</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="L11" s="6">
-        <v>3500</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>80</v>
-      </c>
     </row>
-    <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
       <c r="B12" s="7">
         <v>46118</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>82</v>
+      <c r="C12" s="7"/>
+      <c r="D12" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="K12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="3" t="s">
+      <c r="M12" s="6">
+        <v>750000</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L12" s="6">
-        <v>750000</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P12" s="1"/>
+      <c r="P12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
       <c r="B13" s="7">
         <v>46113</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="M13" s="6">
         <v>15000</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="N13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P13" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
       <c r="B14" s="7">
         <v>46114</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L14" s="6">
+        <v>98</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="M14" s="6">
         <v>50</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>101</v>
+      <c r="N14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
       <c r="B15" s="7">
         <v>46118</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="J15" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="K15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="M15" s="6">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P15" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q15" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O15" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="P15" s="15" t="s">
-        <v>109</v>
-      </c>
     </row>
-    <row r="16" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
       <c r="B16" s="7">
         <v>46115</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="H16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="K16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L16" s="6">
+      <c r="M16" s="6">
         <v>0</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="N16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P16" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
       <c r="B17" s="7">
         <v>46107</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="K17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L17" s="6">
+      <c r="M17" s="6">
         <v>30000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="N17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P17" s="15"/>
+        <v>21</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q17" s="15"/>
     </row>
-    <row r="18" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
       <c r="B18" s="7">
         <v>46206</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="J18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="M18" s="6">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L18" s="6">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N18" s="3" t="s">
+      <c r="P18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="O18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P18" s="15" t="s">
-        <v>128</v>
-      </c>
     </row>
-    <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
       <c r="B19" s="7">
         <v>46219</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>134</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="L19" s="6">
+      <c r="M19" s="6">
         <v>200000</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="N19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P19" s="1"/>
+      <c r="P19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
       <c r="B20" s="7">
         <v>46219</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="H20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L20" s="6">
+        <v>136</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M20" s="6">
         <v>400000</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="N20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P20" s="1"/>
+      <c r="P20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
       <c r="B21" s="7">
         <v>46219</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="K21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L21" s="6">
+      <c r="M21" s="6">
         <v>0</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="N21" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P21" s="16" t="s">
-        <v>142</v>
+        <v>21</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
       <c r="B22" s="7">
         <v>46227</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="7"/>
+      <c r="D22" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="H22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="M22" s="6">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P22" s="1"/>
+      <c r="P22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
       <c r="B23" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="M23" s="6">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="L23" s="6">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P23" s="1"/>
+      <c r="P23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
       <c r="B24" s="7">
         <v>46228</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>152</v>
+      <c r="C24" s="7"/>
+      <c r="D24" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="H24" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="J24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L24" s="6">
+      <c r="M24" s="6">
         <v>2100000</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="N24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P24" s="1"/>
+      <c r="P24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:16" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
       <c r="B25" s="7">
         <v>46233</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="7"/>
+      <c r="D25" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="H25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H25" s="26" t="s">
+      <c r="J25" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="K25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="3" t="s">
+      <c r="M25" s="6">
+        <v>150000</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L25" s="6">
-        <v>150000</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N25" s="3" t="s">
+      <c r="P25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="O25" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P25" s="27" t="s">
-        <v>174</v>
-      </c>
     </row>
-    <row r="26" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
       <c r="B26" s="7">
         <v>46244</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="C26" s="7"/>
+      <c r="D26" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="G26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="K26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K26" s="5" t="s">
+      <c r="M26" s="6">
+        <v>18000</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q26" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="L26" s="6">
-        <v>18000</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P26" s="27" t="s">
-        <v>181</v>
-      </c>
     </row>
-    <row r="27" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
       <c r="B27" s="7">
         <v>44552</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="H27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="3" t="s">
+      <c r="M27" s="6">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q27" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="L27" s="6">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P27" s="15" t="s">
-        <v>189</v>
-      </c>
     </row>
-    <row r="28" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
       <c r="B28" s="7">
         <v>44553</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="M28" s="6">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="L28" s="6">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P28" s="28" t="s">
-        <v>194</v>
-      </c>
     </row>
-    <row r="29" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
       <c r="B29" s="7">
         <v>44566</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="C29" s="7"/>
+      <c r="D29" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="K29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L29" s="6">
+      <c r="M29" s="6">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O29" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P29" s="28" t="s">
-        <v>194</v>
+      <c r="Q29" s="28" t="s">
+        <v>193</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
       <c r="B30" s="7">
         <v>44650</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="C30" s="7"/>
+      <c r="D30" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="H30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="M30" s="6">
         <v>0</v>
       </c>
-      <c r="M30" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N30" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O30" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P30" s="28" t="s">
-        <v>273</v>
+      <c r="Q30" s="28" t="s">
+        <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
       <c r="B31" s="7">
         <v>44830</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="C31" s="7"/>
+      <c r="D31" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="H31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="K31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K31" s="3" t="s">
+      <c r="M31" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="L31" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P31" s="29" t="s">
-        <v>207</v>
-      </c>
     </row>
-    <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
       <c r="B32" s="7">
         <v>44903</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="C32" s="7">
+        <v>46261</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="H32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L32" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="5" t="s">
+      <c r="M32" s="6">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q32" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="L32" s="6">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P32" s="15" t="s">
-        <v>211</v>
-      </c>
     </row>
-    <row r="33" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
       <c r="B33" s="7">
         <v>44931</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="C33" s="7">
+        <v>46261</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="3" t="s">
+      <c r="M33" s="6">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q33" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="L33" s="6">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P33" s="15" t="s">
-        <v>214</v>
-      </c>
     </row>
-    <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
       <c r="B34" s="7">
         <v>44930</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="C34" s="7"/>
+      <c r="D34" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="H34" s="3" t="s">
-        <v>186</v>
+        <v>40</v>
       </c>
       <c r="I34" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="L34" s="6">
+      <c r="M34" s="6">
         <v>0</v>
       </c>
-      <c r="M34" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P34" s="15" t="s">
-        <v>218</v>
+      <c r="Q34" s="15" t="s">
+        <v>217</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
       <c r="B35" s="7">
         <v>44935</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="C35" s="7"/>
+      <c r="D35" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="H35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="L35" s="6">
+      <c r="K35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="M35" s="6">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P35" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P35" s="15" t="s">
-        <v>217</v>
+      <c r="Q35" s="15" t="s">
+        <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
       <c r="B36" s="7">
         <v>44937</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="C36" s="7"/>
+      <c r="D36" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="H36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="K36" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="L36" s="6">
+        <v>19</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="M36" s="6">
         <v>0</v>
       </c>
-      <c r="M36" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P36" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P36" s="15" t="s">
-        <v>220</v>
+      <c r="Q36" s="15" t="s">
+        <v>219</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
       <c r="B37" s="7">
         <v>44938</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="7"/>
+      <c r="D37" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="H37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="L37" s="6">
+      <c r="M37" s="6">
         <v>0</v>
       </c>
-      <c r="M37" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P37" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O37" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P37" s="15" t="s">
-        <v>272</v>
+      <c r="Q37" s="15" t="s">
+        <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
       <c r="B38" s="7">
         <v>44938</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="C38" s="7"/>
+      <c r="D38" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="H38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="L38" s="6">
+      <c r="M38" s="6">
         <v>0</v>
       </c>
-      <c r="M38" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O38" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P38" s="15" t="s">
-        <v>270</v>
+      <c r="Q38" s="15" t="s">
+        <v>269</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
       <c r="B39" s="7">
         <v>45740</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="C39" s="7"/>
+      <c r="D39" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I39" s="3" t="s">
+      <c r="J39" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L39" s="6">
+      <c r="M39" s="6">
         <v>400000</v>
       </c>
-      <c r="M39" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P39" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P39" s="30" t="s">
-        <v>271</v>
+      <c r="Q39" s="30" t="s">
+        <v>270</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
       <c r="B40" s="7">
         <v>45827</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>231</v>
+      <c r="C40" s="7"/>
+      <c r="D40" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H40" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="M40" s="6">
+        <v>400000</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q40" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L40" s="6">
-        <v>400000</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P40" s="30" t="s">
-        <v>230</v>
-      </c>
     </row>
-    <row r="41" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
       <c r="B41" s="7">
         <v>46244</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="C41" s="7"/>
+      <c r="D41" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="H41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="J41" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="K41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L41" s="6">
+      <c r="M41" s="6">
         <v>400000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O41" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P41" s="30" t="s">
-        <v>269</v>
+      <c r="Q41" s="30" t="s">
+        <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>39</v>
       </c>
       <c r="B42" s="7">
         <v>46244</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="C42" s="7"/>
+      <c r="D42" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="K42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L42" s="6">
+      <c r="M42" s="6">
         <v>400000</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P42" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O42" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P42" s="30" t="s">
-        <v>268</v>
+      <c r="Q42" s="30" t="s">
+        <v>267</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
       <c r="B43" s="7">
         <v>46244</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="7"/>
+      <c r="D43" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="G43" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H43" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G43" s="25" t="s">
+      <c r="I43" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="L43" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="M43" s="6">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="L43" s="6">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P43" s="27" t="s">
-        <v>240</v>
-      </c>
     </row>
-    <row r="44" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
       <c r="B44" s="7">
         <v>46244</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="7"/>
+      <c r="D44" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="F44" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="J44" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="K44" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K44" s="3" t="s">
+      <c r="M44" s="6">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q44" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="L44" s="6">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O44" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P44" s="27" t="s">
-        <v>250</v>
-      </c>
     </row>
-    <row r="45" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
       <c r="B45" s="7">
         <v>46246</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="7"/>
+      <c r="D45" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="H45" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="I45" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="K45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="J45" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K45" s="3" t="s">
+      <c r="M45" s="6">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q45" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="L45" s="6">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O45" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P45" s="27" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="46" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
       <c r="B46" s="7">
         <v>46260</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="7"/>
+      <c r="D46" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="F46" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="G46" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="H46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H46" s="3" t="s">
+      <c r="J46" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="K46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K46" s="3" t="s">
+      <c r="M46" s="6">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P46" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q46" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="L46" s="6">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O46" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="P46" s="15" t="s">
-        <v>267</v>
-      </c>
     </row>
-    <row r="47" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="4"/>
+      <c r="D47" s="7"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -5489,17 +5545,18 @@
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="6"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="1"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="1"/>
     </row>
-    <row r="48" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="4"/>
+      <c r="D48" s="7"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -5507,17 +5564,18 @@
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="6"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="1"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="4"/>
+      <c r="D49" s="7"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -5525,17 +5583,18 @@
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="6"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="1"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="4"/>
+      <c r="D50" s="7"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -5543,17 +5602,18 @@
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="6"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="1"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="4"/>
+      <c r="D51" s="7"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -5561,17 +5621,18 @@
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="6"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
-      <c r="P51" s="1"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="4"/>
+      <c r="D52" s="7"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
@@ -5579,17 +5640,18 @@
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="6"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="1"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="4"/>
+      <c r="D53" s="7"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
@@ -5597,17 +5659,18 @@
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="6"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="1"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="1"/>
     </row>
-    <row r="54" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="4"/>
+      <c r="D54" s="7"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -5615,17 +5678,18 @@
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="6"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="1"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="4"/>
+      <c r="D55" s="7"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -5633,17 +5697,18 @@
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="6"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
-      <c r="P55" s="1"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="1"/>
     </row>
-    <row r="56" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="4"/>
+      <c r="D56" s="7"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -5651,20 +5716,21 @@
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="6"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="1"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="1"/>
     </row>
-    <row r="57" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6601,7 +6667,7 @@
     <row r="998" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A3:P13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A3:Q13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/^N^N 시설관리유지보수 (독립)/facility/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="522" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{741B5F8D-5536-4FA6-8CBB-04B3FA65F560}"/>
+  <xr:revisionPtr revIDLastSave="566" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFEA1D08-6FDC-4AB3-A096-587B0FC6378A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="276">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2787,6 +2787,10 @@
   </si>
   <si>
     <t>수리완료일자</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>25/628</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3080,10 +3084,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3373,7 +3373,9 @@
       <c r="B4" s="7">
         <v>46056</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="7">
+        <v>46067</v>
+      </c>
       <c r="D4" s="13" t="s">
         <v>42</v>
       </c>
@@ -3422,7 +3424,9 @@
       <c r="B5" s="7">
         <v>46064</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="7">
+        <v>46064</v>
+      </c>
       <c r="D5" s="13" t="s">
         <v>42</v>
       </c>
@@ -3473,7 +3477,9 @@
       <c r="B6" s="7">
         <v>46058</v>
       </c>
-      <c r="C6" s="7"/>
+      <c r="C6" s="7">
+        <v>46058</v>
+      </c>
       <c r="D6" s="13" t="s">
         <v>42</v>
       </c>
@@ -3522,7 +3528,9 @@
       <c r="B7" s="7">
         <v>46063</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="7">
+        <v>46068</v>
+      </c>
       <c r="D7" s="13" t="s">
         <v>43</v>
       </c>
@@ -3571,7 +3579,9 @@
       <c r="B8" s="7">
         <v>46073</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="7">
+        <v>46077</v>
+      </c>
       <c r="D8" s="13" t="s">
         <v>43</v>
       </c>
@@ -3620,7 +3630,9 @@
       <c r="B9" s="7">
         <v>46091</v>
       </c>
-      <c r="C9" s="7"/>
+      <c r="C9" s="7">
+        <v>46096</v>
+      </c>
       <c r="D9" s="13" t="s">
         <v>57</v>
       </c>
@@ -3669,7 +3681,9 @@
       <c r="B10" s="7">
         <v>46093</v>
       </c>
-      <c r="C10" s="7"/>
+      <c r="C10" s="7">
+        <v>46099</v>
+      </c>
       <c r="D10" s="13" t="s">
         <v>42</v>
       </c>
@@ -3718,7 +3732,9 @@
       <c r="B11" s="7">
         <v>46114</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="7">
+        <v>46126</v>
+      </c>
       <c r="D11" s="13" t="s">
         <v>71</v>
       </c>
@@ -3769,7 +3785,9 @@
       <c r="B12" s="7">
         <v>46118</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="7">
+        <v>46130</v>
+      </c>
       <c r="D12" s="13" t="s">
         <v>42</v>
       </c>
@@ -3818,7 +3836,9 @@
       <c r="B13" s="7">
         <v>46113</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="7">
+        <v>46130</v>
+      </c>
       <c r="D13" s="13" t="s">
         <v>57</v>
       </c>
@@ -3867,7 +3887,9 @@
       <c r="B14" s="7">
         <v>46114</v>
       </c>
-      <c r="C14" s="7"/>
+      <c r="C14" s="7">
+        <v>46122</v>
+      </c>
       <c r="D14" s="13" t="s">
         <v>71</v>
       </c>
@@ -3918,7 +3940,9 @@
       <c r="B15" s="7">
         <v>46118</v>
       </c>
-      <c r="C15" s="7"/>
+      <c r="C15" s="7">
+        <v>46118</v>
+      </c>
       <c r="D15" s="13" t="s">
         <v>42</v>
       </c>
@@ -3969,7 +3993,9 @@
       <c r="B16" s="7">
         <v>46115</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="7">
+        <v>46120</v>
+      </c>
       <c r="D16" s="13" t="s">
         <v>57</v>
       </c>
@@ -4018,7 +4044,9 @@
       <c r="B17" s="7">
         <v>46107</v>
       </c>
-      <c r="C17" s="7"/>
+      <c r="C17" s="7">
+        <v>46116</v>
+      </c>
       <c r="D17" s="13" t="s">
         <v>117</v>
       </c>
@@ -4067,7 +4095,9 @@
       <c r="B18" s="7">
         <v>46206</v>
       </c>
-      <c r="C18" s="7"/>
+      <c r="C18" s="7">
+        <v>46213</v>
+      </c>
       <c r="D18" s="13" t="s">
         <v>57</v>
       </c>
@@ -4118,7 +4148,9 @@
       <c r="B19" s="7">
         <v>46219</v>
       </c>
-      <c r="C19" s="7"/>
+      <c r="C19" s="7">
+        <v>46219</v>
+      </c>
       <c r="D19" s="13" t="s">
         <v>128</v>
       </c>
@@ -4167,7 +4199,9 @@
       <c r="B20" s="7">
         <v>46219</v>
       </c>
-      <c r="C20" s="7"/>
+      <c r="C20" s="7">
+        <v>46219</v>
+      </c>
       <c r="D20" s="13" t="s">
         <v>43</v>
       </c>
@@ -4216,7 +4250,9 @@
       <c r="B21" s="7">
         <v>46219</v>
       </c>
-      <c r="C21" s="7"/>
+      <c r="C21" s="7">
+        <v>46227</v>
+      </c>
       <c r="D21" s="13" t="s">
         <v>57</v>
       </c>
@@ -4267,7 +4303,9 @@
       <c r="B22" s="7">
         <v>46227</v>
       </c>
-      <c r="C22" s="7"/>
+      <c r="C22" s="7">
+        <v>46231</v>
+      </c>
       <c r="D22" s="13" t="s">
         <v>144</v>
       </c>
@@ -4316,7 +4354,9 @@
       <c r="B23" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="24"/>
+      <c r="C23" s="24">
+        <v>46235</v>
+      </c>
       <c r="D23" s="13" t="s">
         <v>144</v>
       </c>
@@ -4365,7 +4405,9 @@
       <c r="B24" s="7">
         <v>46228</v>
       </c>
-      <c r="C24" s="7"/>
+      <c r="C24" s="7">
+        <v>46244</v>
+      </c>
       <c r="D24" s="13" t="s">
         <v>144</v>
       </c>
@@ -4414,7 +4456,9 @@
       <c r="B25" s="7">
         <v>46233</v>
       </c>
-      <c r="C25" s="7"/>
+      <c r="C25" s="7">
+        <v>46242</v>
+      </c>
       <c r="D25" s="13" t="s">
         <v>165</v>
       </c>
@@ -4465,7 +4509,9 @@
       <c r="B26" s="7">
         <v>46244</v>
       </c>
-      <c r="C26" s="7"/>
+      <c r="C26" s="7">
+        <v>46252</v>
+      </c>
       <c r="D26" s="13" t="s">
         <v>42</v>
       </c>
@@ -4516,7 +4562,9 @@
       <c r="B27" s="7">
         <v>44552</v>
       </c>
-      <c r="C27" s="7"/>
+      <c r="C27" s="7">
+        <v>44558</v>
+      </c>
       <c r="D27" s="13" t="s">
         <v>182</v>
       </c>
@@ -4567,7 +4615,9 @@
       <c r="B28" s="7">
         <v>44553</v>
       </c>
-      <c r="C28" s="7"/>
+      <c r="C28" s="7">
+        <v>44558</v>
+      </c>
       <c r="D28" s="13" t="s">
         <v>182</v>
       </c>
@@ -4618,7 +4668,9 @@
       <c r="B29" s="7">
         <v>44566</v>
       </c>
-      <c r="C29" s="7"/>
+      <c r="C29" s="7">
+        <v>44571</v>
+      </c>
       <c r="D29" s="13" t="s">
         <v>42</v>
       </c>
@@ -4669,7 +4721,9 @@
       <c r="B30" s="7">
         <v>44650</v>
       </c>
-      <c r="C30" s="7"/>
+      <c r="C30" s="7">
+        <v>44655</v>
+      </c>
       <c r="D30" s="13" t="s">
         <v>42</v>
       </c>
@@ -4720,7 +4774,9 @@
       <c r="B31" s="7">
         <v>44830</v>
       </c>
-      <c r="C31" s="7"/>
+      <c r="C31" s="7">
+        <v>44838</v>
+      </c>
       <c r="D31" s="13" t="s">
         <v>182</v>
       </c>
@@ -4772,7 +4828,7 @@
         <v>44903</v>
       </c>
       <c r="C32" s="7">
-        <v>46261</v>
+        <v>44905</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>42</v>
@@ -4825,7 +4881,7 @@
         <v>44931</v>
       </c>
       <c r="C33" s="7">
-        <v>46261</v>
+        <v>44940</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>42</v>
@@ -4877,7 +4933,9 @@
       <c r="B34" s="7">
         <v>44930</v>
       </c>
-      <c r="C34" s="7"/>
+      <c r="C34" s="7">
+        <v>44940</v>
+      </c>
       <c r="D34" s="13" t="s">
         <v>42</v>
       </c>
@@ -4928,7 +4986,9 @@
       <c r="B35" s="7">
         <v>44935</v>
       </c>
-      <c r="C35" s="7"/>
+      <c r="C35" s="7">
+        <v>44940</v>
+      </c>
       <c r="D35" s="13" t="s">
         <v>182</v>
       </c>
@@ -4979,7 +5039,9 @@
       <c r="B36" s="7">
         <v>44937</v>
       </c>
-      <c r="C36" s="7"/>
+      <c r="C36" s="7">
+        <v>44941</v>
+      </c>
       <c r="D36" s="13" t="s">
         <v>182</v>
       </c>
@@ -5030,7 +5092,9 @@
       <c r="B37" s="7">
         <v>44938</v>
       </c>
-      <c r="C37" s="7"/>
+      <c r="C37" s="7">
+        <v>44944</v>
+      </c>
       <c r="D37" s="13" t="s">
         <v>182</v>
       </c>
@@ -5081,7 +5145,9 @@
       <c r="B38" s="7">
         <v>44938</v>
       </c>
-      <c r="C38" s="7"/>
+      <c r="C38" s="7">
+        <v>44944</v>
+      </c>
       <c r="D38" s="13" t="s">
         <v>182</v>
       </c>
@@ -5132,7 +5198,9 @@
       <c r="B39" s="7">
         <v>45740</v>
       </c>
-      <c r="C39" s="7"/>
+      <c r="C39" s="7">
+        <v>45751</v>
+      </c>
       <c r="D39" s="13" t="s">
         <v>182</v>
       </c>
@@ -5183,7 +5251,9 @@
       <c r="B40" s="7">
         <v>45827</v>
       </c>
-      <c r="C40" s="7"/>
+      <c r="C40" s="24" t="s">
+        <v>275</v>
+      </c>
       <c r="D40" s="13" t="s">
         <v>182</v>
       </c>
@@ -5234,7 +5304,9 @@
       <c r="B41" s="7">
         <v>46244</v>
       </c>
-      <c r="C41" s="7"/>
+      <c r="C41" s="7">
+        <v>46261</v>
+      </c>
       <c r="D41" s="13" t="s">
         <v>182</v>
       </c>
@@ -5285,7 +5357,9 @@
       <c r="B42" s="7">
         <v>46244</v>
       </c>
-      <c r="C42" s="7"/>
+      <c r="C42" s="7">
+        <v>46261</v>
+      </c>
       <c r="D42" s="13" t="s">
         <v>182</v>
       </c>
@@ -5336,7 +5410,9 @@
       <c r="B43" s="7">
         <v>46244</v>
       </c>
-      <c r="C43" s="7"/>
+      <c r="C43" s="7">
+        <v>46246</v>
+      </c>
       <c r="D43" s="13" t="s">
         <v>231</v>
       </c>
@@ -5387,7 +5463,9 @@
       <c r="B44" s="7">
         <v>46244</v>
       </c>
-      <c r="C44" s="7"/>
+      <c r="C44" s="7">
+        <v>46248</v>
+      </c>
       <c r="D44" s="13" t="s">
         <v>240</v>
       </c>
@@ -5438,7 +5516,9 @@
       <c r="B45" s="7">
         <v>46246</v>
       </c>
-      <c r="C45" s="7"/>
+      <c r="C45" s="7">
+        <v>46252</v>
+      </c>
       <c r="D45" s="13" t="s">
         <v>250</v>
       </c>
@@ -5489,7 +5569,9 @@
       <c r="B46" s="7">
         <v>46260</v>
       </c>
-      <c r="C46" s="7"/>
+      <c r="C46" s="7">
+        <v>46260</v>
+      </c>
       <c r="D46" s="13" t="s">
         <v>259</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/^N^N 시설관리유지보수 (독립)/facility/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="566" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFEA1D08-6FDC-4AB3-A096-587B0FC6378A}"/>
+  <xr:revisionPtr revIDLastSave="580" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{742038CC-4CB0-492F-8783-0B86EFFEAA45}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="sa" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$V$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="281">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2791,6 +2791,26 @@
   </si>
   <si>
     <t>25/628</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정이슈 발생일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정이슈 발생이력</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정이슈 발생 종료일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 이슈 내용</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정이슈 증빙자료</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3283,7 +3303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q999"/>
+  <dimension ref="A1:V999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="20" customWidth="1"/>
@@ -3302,18 +3322,19 @@
     <col min="14" max="14" width="15.28515625" style="20" customWidth="1"/>
     <col min="15" max="15" width="10.28515625" style="20" customWidth="1"/>
     <col min="16" max="16" width="14.28515625" style="20" customWidth="1"/>
-    <col min="17" max="17" width="87.85546875" customWidth="1"/>
-    <col min="18" max="30" width="6.5703125" customWidth="1"/>
+    <col min="17" max="21" width="30.28515625" style="20" customWidth="1"/>
+    <col min="22" max="22" width="87.85546875" customWidth="1"/>
+    <col min="23" max="35" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>30</v>
       </c>
       <c r="E1" s="19"/>
     </row>
-    <row r="2" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
@@ -3363,10 +3384,25 @@
         <v>14</v>
       </c>
       <c r="Q3" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -3415,9 +3451,14 @@
       <c r="P4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="4"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -3466,11 +3507,16 @@
       <c r="P5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -3519,9 +3565,14 @@
       <c r="P6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" s="4"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -3570,9 +3621,14 @@
       <c r="P7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q7" s="4"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="4"/>
     </row>
-    <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -3621,9 +3677,14 @@
       <c r="P8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="4"/>
     </row>
-    <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -3672,9 +3733,14 @@
       <c r="P9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="4"/>
     </row>
-    <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -3723,9 +3789,14 @@
       <c r="P10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="4"/>
     </row>
-    <row r="11" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -3774,11 +3845,16 @@
       <c r="P11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q11" s="16" t="s">
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="16" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -3827,9 +3903,14 @@
       <c r="P12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q12" s="1"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -3878,9 +3959,14 @@
       <c r="P13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -3929,11 +4015,16 @@
       <c r="P14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q14" s="15" t="s">
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -3982,11 +4073,16 @@
       <c r="P15" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="Q15" s="15" t="s">
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -4035,9 +4131,14 @@
       <c r="P16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q16" s="1"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -4086,9 +4187,14 @@
       <c r="P17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q17" s="15"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="15"/>
     </row>
-    <row r="18" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -4137,11 +4243,16 @@
       <c r="P18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q18" s="15" t="s">
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="15" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -4190,9 +4301,14 @@
       <c r="P19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q19" s="1"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -4241,9 +4357,14 @@
       <c r="P20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q20" s="1"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -4292,11 +4413,16 @@
       <c r="P21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q21" s="16" t="s">
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="16" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -4345,9 +4471,14 @@
       <c r="P22" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q22" s="1"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -4396,9 +4527,14 @@
       <c r="P23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q23" s="1"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -4447,9 +4583,14 @@
       <c r="P24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q24" s="1"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -4498,11 +4639,16 @@
       <c r="P25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q25" s="27" t="s">
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="27" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -4551,11 +4697,16 @@
       <c r="P26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q26" s="27" t="s">
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="27" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -4604,11 +4755,16 @@
       <c r="P27" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q27" s="15" t="s">
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="15" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -4657,11 +4813,16 @@
       <c r="P28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q28" s="28" t="s">
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="28" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -4710,11 +4871,16 @@
       <c r="P29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q29" s="28" t="s">
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="28" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -4763,11 +4929,16 @@
       <c r="P30" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q30" s="28" t="s">
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="28" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -4816,11 +4987,16 @@
       <c r="P31" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q31" s="29" t="s">
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="29" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -4869,11 +5045,16 @@
       <c r="P32" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q32" s="15" t="s">
+      <c r="Q32" s="8"/>
+      <c r="R32" s="8"/>
+      <c r="S32" s="8"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="8"/>
+      <c r="V32" s="15" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -4922,11 +5103,16 @@
       <c r="P33" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q33" s="15" t="s">
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="15" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -4975,11 +5161,16 @@
       <c r="P34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q34" s="15" t="s">
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="8"/>
+      <c r="V34" s="15" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -5028,11 +5219,16 @@
       <c r="P35" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q35" s="15" t="s">
+      <c r="Q35" s="8"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="8"/>
+      <c r="V35" s="15" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -5081,11 +5277,16 @@
       <c r="P36" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q36" s="15" t="s">
+      <c r="Q36" s="8"/>
+      <c r="R36" s="8"/>
+      <c r="S36" s="8"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="8"/>
+      <c r="V36" s="15" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -5134,11 +5335,16 @@
       <c r="P37" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q37" s="15" t="s">
+      <c r="Q37" s="8"/>
+      <c r="R37" s="8"/>
+      <c r="S37" s="8"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="8"/>
+      <c r="V37" s="15" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -5187,11 +5393,16 @@
       <c r="P38" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q38" s="15" t="s">
+      <c r="Q38" s="8"/>
+      <c r="R38" s="8"/>
+      <c r="S38" s="8"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="8"/>
+      <c r="V38" s="15" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -5240,11 +5451,16 @@
       <c r="P39" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q39" s="30" t="s">
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8"/>
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="8"/>
+      <c r="V39" s="30" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -5293,11 +5509,16 @@
       <c r="P40" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q40" s="30" t="s">
+      <c r="Q40" s="8"/>
+      <c r="R40" s="8"/>
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="8"/>
+      <c r="V40" s="30" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -5346,11 +5567,16 @@
       <c r="P41" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q41" s="30" t="s">
+      <c r="Q41" s="8"/>
+      <c r="R41" s="8"/>
+      <c r="S41" s="8"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="8"/>
+      <c r="V41" s="30" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -5399,11 +5625,16 @@
       <c r="P42" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q42" s="30" t="s">
+      <c r="Q42" s="8"/>
+      <c r="R42" s="8"/>
+      <c r="S42" s="8"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="8"/>
+      <c r="V42" s="30" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -5452,11 +5683,16 @@
       <c r="P43" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q43" s="27" t="s">
+      <c r="Q43" s="8"/>
+      <c r="R43" s="8"/>
+      <c r="S43" s="8"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="8"/>
+      <c r="V43" s="27" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -5505,11 +5741,16 @@
       <c r="P44" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q44" s="27" t="s">
+      <c r="Q44" s="8"/>
+      <c r="R44" s="8"/>
+      <c r="S44" s="8"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="8"/>
+      <c r="V44" s="27" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -5558,11 +5799,16 @@
       <c r="P45" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q45" s="27" t="s">
+      <c r="Q45" s="8"/>
+      <c r="R45" s="8"/>
+      <c r="S45" s="8"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="8"/>
+      <c r="V45" s="27" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -5611,11 +5857,16 @@
       <c r="P46" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="Q46" s="15" t="s">
+      <c r="Q46" s="22"/>
+      <c r="R46" s="22"/>
+      <c r="S46" s="22"/>
+      <c r="T46" s="22"/>
+      <c r="U46" s="22"/>
+      <c r="V46" s="15" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -5632,9 +5883,14 @@
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
       <c r="P47" s="4"/>
-      <c r="Q47" s="1"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -5651,9 +5907,14 @@
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
       <c r="P48" s="4"/>
-      <c r="Q48" s="1"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -5670,9 +5931,14 @@
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
       <c r="P49" s="4"/>
-      <c r="Q49" s="1"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -5689,9 +5955,14 @@
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
       <c r="P50" s="4"/>
-      <c r="Q50" s="1"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -5708,9 +5979,14 @@
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
       <c r="P51" s="4"/>
-      <c r="Q51" s="1"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -5727,9 +6003,14 @@
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
       <c r="P52" s="4"/>
-      <c r="Q52" s="1"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -5746,9 +6027,14 @@
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
       <c r="P53" s="4"/>
-      <c r="Q53" s="1"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -5765,9 +6051,14 @@
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
       <c r="P54" s="4"/>
-      <c r="Q54" s="1"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -5784,9 +6075,14 @@
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
       <c r="P55" s="4"/>
-      <c r="Q55" s="1"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -5803,16 +6099,21 @@
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
       <c r="P56" s="4"/>
-      <c r="Q56" s="1"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6749,7 +7050,7 @@
     <row r="998" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A3:Q13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A3:V13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="580" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{742038CC-4CB0-492F-8783-0B86EFFEAA45}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C7938FF-2FDA-4C14-B99E-1093524E37AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="290">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2811,6 +2811,72 @@
   </si>
   <si>
     <t>특정이슈 증빙자료</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 화물리프트</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>화물리프트</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO26</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>월간유지보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상 없음</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 정기 점검 진행</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">승강기 유지보수료 인상의 건(월10,000원 인상) - 자재비 등 물가 상승으로 인한 월 유지 보수료 인상 요인 발생 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2993,7 +3059,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3087,6 +3153,24 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3102,6 +3186,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3313,7 +3401,7 @@
     <col min="5" max="5" width="33" style="20" customWidth="1"/>
     <col min="6" max="6" width="31.140625" style="20" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" style="20" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" style="20" customWidth="1"/>
     <col min="9" max="9" width="28.5703125" style="20" customWidth="1"/>
     <col min="10" max="10" width="42" style="20" customWidth="1"/>
     <col min="11" max="11" width="21" style="20" customWidth="1"/>
@@ -3322,7 +3410,10 @@
     <col min="14" max="14" width="15.28515625" style="20" customWidth="1"/>
     <col min="15" max="15" width="10.28515625" style="20" customWidth="1"/>
     <col min="16" max="16" width="14.28515625" style="20" customWidth="1"/>
-    <col min="17" max="21" width="30.28515625" style="20" customWidth="1"/>
+    <col min="17" max="18" width="30.28515625" style="20" customWidth="1"/>
+    <col min="19" max="19" width="30.28515625" style="33" customWidth="1"/>
+    <col min="20" max="20" width="30.28515625" style="20" customWidth="1"/>
+    <col min="21" max="21" width="30.28515625" style="33" customWidth="1"/>
     <col min="22" max="22" width="87.85546875" customWidth="1"/>
     <col min="23" max="35" width="6.5703125" customWidth="1"/>
   </cols>
@@ -3389,13 +3480,13 @@
       <c r="R3" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="34" t="s">
         <v>276</v>
       </c>
       <c r="T3" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="U3" s="34" t="s">
         <v>278</v>
       </c>
       <c r="V3" s="11" t="s">
@@ -3453,9 +3544,9 @@
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
+      <c r="S4" s="35"/>
       <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
+      <c r="U4" s="35"/>
       <c r="V4" s="4"/>
     </row>
     <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3509,9 +3600,9 @@
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
+      <c r="S5" s="35"/>
       <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
+      <c r="U5" s="35"/>
       <c r="V5" s="2" t="s">
         <v>29</v>
       </c>
@@ -3567,9 +3658,9 @@
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
+      <c r="S6" s="35"/>
       <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
+      <c r="U6" s="35"/>
       <c r="V6" s="4"/>
     </row>
     <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3623,9 +3714,9 @@
       </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
+      <c r="S7" s="35"/>
       <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
+      <c r="U7" s="35"/>
       <c r="V7" s="4"/>
     </row>
     <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3679,9 +3770,9 @@
       </c>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
+      <c r="S8" s="35"/>
       <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
+      <c r="U8" s="35"/>
       <c r="V8" s="4"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3735,9 +3826,9 @@
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
+      <c r="S9" s="35"/>
       <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
+      <c r="U9" s="35"/>
       <c r="V9" s="4"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3791,9 +3882,9 @@
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
+      <c r="S10" s="35"/>
       <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
+      <c r="U10" s="35"/>
       <c r="V10" s="4"/>
     </row>
     <row r="11" spans="1:22" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3847,9 +3938,9 @@
       </c>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
+      <c r="S11" s="35"/>
       <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
+      <c r="U11" s="35"/>
       <c r="V11" s="16" t="s">
         <v>79</v>
       </c>
@@ -3905,9 +3996,9 @@
       </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
+      <c r="S12" s="35"/>
       <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
+      <c r="U12" s="35"/>
       <c r="V12" s="1"/>
     </row>
     <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3961,9 +4052,9 @@
       </c>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
+      <c r="S13" s="35"/>
       <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
+      <c r="U13" s="35"/>
       <c r="V13" s="1"/>
     </row>
     <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4017,9 +4108,9 @@
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
+      <c r="S14" s="35"/>
       <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
+      <c r="U14" s="35"/>
       <c r="V14" s="15" t="s">
         <v>100</v>
       </c>
@@ -4075,9 +4166,9 @@
       </c>
       <c r="Q15" s="22"/>
       <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
+      <c r="S15" s="36"/>
       <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
+      <c r="U15" s="36"/>
       <c r="V15" s="15" t="s">
         <v>108</v>
       </c>
@@ -4133,9 +4224,9 @@
       </c>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
+      <c r="S16" s="35"/>
       <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
+      <c r="U16" s="35"/>
       <c r="V16" s="1"/>
     </row>
     <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4189,9 +4280,9 @@
       </c>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
+      <c r="S17" s="35"/>
       <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
+      <c r="U17" s="35"/>
       <c r="V17" s="15"/>
     </row>
     <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4245,9 +4336,9 @@
       </c>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
+      <c r="S18" s="35"/>
       <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
+      <c r="U18" s="35"/>
       <c r="V18" s="15" t="s">
         <v>127</v>
       </c>
@@ -4303,9 +4394,9 @@
       </c>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
+      <c r="S19" s="35"/>
       <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
+      <c r="U19" s="35"/>
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4359,9 +4450,9 @@
       </c>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
+      <c r="S20" s="35"/>
       <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
+      <c r="U20" s="35"/>
       <c r="V20" s="1"/>
     </row>
     <row r="21" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4415,9 +4506,9 @@
       </c>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
+      <c r="S21" s="35"/>
       <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
+      <c r="U21" s="35"/>
       <c r="V21" s="16" t="s">
         <v>141</v>
       </c>
@@ -4473,9 +4564,9 @@
       </c>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
+      <c r="S22" s="35"/>
       <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
+      <c r="U22" s="35"/>
       <c r="V22" s="1"/>
     </row>
     <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4529,9 +4620,9 @@
       </c>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
+      <c r="S23" s="35"/>
       <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
+      <c r="U23" s="35"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4585,9 +4676,9 @@
       </c>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
+      <c r="S24" s="35"/>
       <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
+      <c r="U24" s="35"/>
       <c r="V24" s="1"/>
     </row>
     <row r="25" spans="1:22" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4641,9 +4732,9 @@
       </c>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
+      <c r="S25" s="35"/>
       <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
+      <c r="U25" s="35"/>
       <c r="V25" s="27" t="s">
         <v>173</v>
       </c>
@@ -4699,9 +4790,9 @@
       </c>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
+      <c r="S26" s="35"/>
       <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
+      <c r="U26" s="35"/>
       <c r="V26" s="27" t="s">
         <v>180</v>
       </c>
@@ -4757,9 +4848,9 @@
       </c>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
+      <c r="S27" s="35"/>
       <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
+      <c r="U27" s="35"/>
       <c r="V27" s="15" t="s">
         <v>188</v>
       </c>
@@ -4815,9 +4906,9 @@
       </c>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
+      <c r="S28" s="35"/>
       <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
+      <c r="U28" s="35"/>
       <c r="V28" s="28" t="s">
         <v>193</v>
       </c>
@@ -4873,9 +4964,9 @@
       </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
+      <c r="S29" s="35"/>
       <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
+      <c r="U29" s="35"/>
       <c r="V29" s="28" t="s">
         <v>193</v>
       </c>
@@ -4931,9 +5022,9 @@
       </c>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
+      <c r="S30" s="35"/>
       <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
+      <c r="U30" s="35"/>
       <c r="V30" s="28" t="s">
         <v>272</v>
       </c>
@@ -4989,9 +5080,9 @@
       </c>
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
+      <c r="S31" s="35"/>
       <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
+      <c r="U31" s="35"/>
       <c r="V31" s="29" t="s">
         <v>206</v>
       </c>
@@ -5047,9 +5138,9 @@
       </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
+      <c r="S32" s="35"/>
       <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
+      <c r="U32" s="35"/>
       <c r="V32" s="15" t="s">
         <v>210</v>
       </c>
@@ -5105,9 +5196,9 @@
       </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
+      <c r="S33" s="35"/>
       <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
+      <c r="U33" s="35"/>
       <c r="V33" s="15" t="s">
         <v>213</v>
       </c>
@@ -5163,9 +5254,9 @@
       </c>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
+      <c r="S34" s="35"/>
       <c r="T34" s="8"/>
-      <c r="U34" s="8"/>
+      <c r="U34" s="35"/>
       <c r="V34" s="15" t="s">
         <v>217</v>
       </c>
@@ -5221,9 +5312,9 @@
       </c>
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
-      <c r="S35" s="8"/>
+      <c r="S35" s="35"/>
       <c r="T35" s="8"/>
-      <c r="U35" s="8"/>
+      <c r="U35" s="35"/>
       <c r="V35" s="15" t="s">
         <v>216</v>
       </c>
@@ -5279,9 +5370,9 @@
       </c>
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
+      <c r="S36" s="35"/>
       <c r="T36" s="8"/>
-      <c r="U36" s="8"/>
+      <c r="U36" s="35"/>
       <c r="V36" s="15" t="s">
         <v>219</v>
       </c>
@@ -5337,9 +5428,9 @@
       </c>
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
-      <c r="S37" s="8"/>
+      <c r="S37" s="35"/>
       <c r="T37" s="8"/>
-      <c r="U37" s="8"/>
+      <c r="U37" s="35"/>
       <c r="V37" s="15" t="s">
         <v>271</v>
       </c>
@@ -5395,9 +5486,9 @@
       </c>
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
-      <c r="S38" s="8"/>
+      <c r="S38" s="35"/>
       <c r="T38" s="8"/>
-      <c r="U38" s="8"/>
+      <c r="U38" s="35"/>
       <c r="V38" s="15" t="s">
         <v>269</v>
       </c>
@@ -5453,9 +5544,9 @@
       </c>
       <c r="Q39" s="8"/>
       <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
+      <c r="S39" s="35"/>
       <c r="T39" s="8"/>
-      <c r="U39" s="8"/>
+      <c r="U39" s="35"/>
       <c r="V39" s="30" t="s">
         <v>270</v>
       </c>
@@ -5511,9 +5602,9 @@
       </c>
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
-      <c r="S40" s="8"/>
+      <c r="S40" s="35"/>
       <c r="T40" s="8"/>
-      <c r="U40" s="8"/>
+      <c r="U40" s="35"/>
       <c r="V40" s="30" t="s">
         <v>229</v>
       </c>
@@ -5569,9 +5660,9 @@
       </c>
       <c r="Q41" s="8"/>
       <c r="R41" s="8"/>
-      <c r="S41" s="8"/>
+      <c r="S41" s="35"/>
       <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
+      <c r="U41" s="35"/>
       <c r="V41" s="30" t="s">
         <v>268</v>
       </c>
@@ -5627,9 +5718,9 @@
       </c>
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
+      <c r="S42" s="35"/>
       <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
+      <c r="U42" s="35"/>
       <c r="V42" s="30" t="s">
         <v>267</v>
       </c>
@@ -5685,9 +5776,9 @@
       </c>
       <c r="Q43" s="8"/>
       <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
+      <c r="S43" s="35"/>
       <c r="T43" s="8"/>
-      <c r="U43" s="8"/>
+      <c r="U43" s="35"/>
       <c r="V43" s="27" t="s">
         <v>239</v>
       </c>
@@ -5743,9 +5834,9 @@
       </c>
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
-      <c r="S44" s="8"/>
+      <c r="S44" s="35"/>
       <c r="T44" s="8"/>
-      <c r="U44" s="8"/>
+      <c r="U44" s="35"/>
       <c r="V44" s="27" t="s">
         <v>249</v>
       </c>
@@ -5801,9 +5892,9 @@
       </c>
       <c r="Q45" s="8"/>
       <c r="R45" s="8"/>
-      <c r="S45" s="8"/>
+      <c r="S45" s="35"/>
       <c r="T45" s="8"/>
-      <c r="U45" s="8"/>
+      <c r="U45" s="35"/>
       <c r="V45" s="27" t="s">
         <v>258</v>
       </c>
@@ -5859,35 +5950,71 @@
       </c>
       <c r="Q46" s="22"/>
       <c r="R46" s="22"/>
-      <c r="S46" s="22"/>
+      <c r="S46" s="36"/>
       <c r="T46" s="22"/>
-      <c r="U46" s="22"/>
+      <c r="U46" s="36"/>
       <c r="V46" s="15" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
+      <c r="A47" s="4">
+        <v>44</v>
+      </c>
+      <c r="B47" s="7">
+        <v>46260</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46260</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="M47" s="6">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P47" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q47" s="26" t="s">
+        <v>289</v>
+      </c>
       <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
+      <c r="S47" s="32">
+        <v>46260</v>
+      </c>
       <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
+      <c r="U47" s="32"/>
       <c r="V47" s="1"/>
     </row>
     <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5909,9 +6036,9 @@
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
+      <c r="S48" s="32"/>
       <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
+      <c r="U48" s="32"/>
       <c r="V48" s="1"/>
     </row>
     <row r="49" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5933,9 +6060,9 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
       <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
+      <c r="S49" s="32"/>
       <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
+      <c r="U49" s="32"/>
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5957,9 +6084,9 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
+      <c r="S50" s="32"/>
       <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
+      <c r="U50" s="32"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5981,9 +6108,9 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
+      <c r="S51" s="32"/>
       <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
+      <c r="U51" s="32"/>
       <c r="V51" s="1"/>
     </row>
     <row r="52" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6005,9 +6132,9 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
+      <c r="S52" s="32"/>
       <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
+      <c r="U52" s="32"/>
       <c r="V52" s="1"/>
     </row>
     <row r="53" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6029,9 +6156,9 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
+      <c r="S53" s="32"/>
       <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
+      <c r="U53" s="32"/>
       <c r="V53" s="1"/>
     </row>
     <row r="54" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6053,9 +6180,9 @@
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
       <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
+      <c r="S54" s="32"/>
       <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
+      <c r="U54" s="32"/>
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6077,9 +6204,9 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
+      <c r="S55" s="32"/>
       <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
+      <c r="U55" s="32"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6101,9 +6228,9 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
       <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
+      <c r="S56" s="32"/>
       <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
+      <c r="U56" s="32"/>
       <c r="V56" s="1"/>
     </row>
     <row r="57" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="603" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C7938FF-2FDA-4C14-B99E-1093524E37AB}"/>
+  <xr:revisionPtr revIDLastSave="605" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7309FD85-4DB5-464E-BF7E-33FB67E4D7CA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2534,10 +2534,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>TO24</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>상.하 작동 레버 파손</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2838,10 +2834,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>TO26</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>월간유지보수</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2877,6 +2869,14 @@
   </si>
   <si>
     <t xml:space="preserve">승강기 유지보수료 인상의 건(월10,000원 인상) - 자재비 등 물가 상승으로 인한 월 유지 보수료 인상 요인 발생 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-24</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-26</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3430,10 +3430,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>41</v>
@@ -3475,19 +3475,19 @@
         <v>14</v>
       </c>
       <c r="Q3" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="R3" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="R3" s="11" t="s">
-        <v>280</v>
-      </c>
       <c r="S3" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="T3" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="U3" s="34" t="s">
         <v>277</v>
-      </c>
-      <c r="U3" s="34" t="s">
-        <v>278</v>
       </c>
       <c r="V3" s="11" t="s">
         <v>10</v>
@@ -5026,7 +5026,7 @@
       <c r="T30" s="8"/>
       <c r="U30" s="35"/>
       <c r="V30" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5432,7 +5432,7 @@
       <c r="T37" s="8"/>
       <c r="U37" s="35"/>
       <c r="V37" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5490,7 +5490,7 @@
       <c r="T38" s="8"/>
       <c r="U38" s="35"/>
       <c r="V38" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5548,7 +5548,7 @@
       <c r="T39" s="8"/>
       <c r="U39" s="35"/>
       <c r="V39" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5559,7 +5559,7 @@
         <v>45827</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>182</v>
@@ -5664,7 +5664,7 @@
       <c r="T41" s="8"/>
       <c r="U41" s="35"/>
       <c r="V41" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5722,7 +5722,7 @@
       <c r="T42" s="8"/>
       <c r="U42" s="35"/>
       <c r="V42" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5919,22 +5919,22 @@
         <v>261</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I46" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M46" s="6">
         <v>0</v>
@@ -5954,7 +5954,7 @@
       <c r="T46" s="22"/>
       <c r="U46" s="36"/>
       <c r="V46" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5968,31 +5968,31 @@
         <v>46260</v>
       </c>
       <c r="D47" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="I47" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="J47" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="M47" s="6">
         <v>0</v>
@@ -6004,10 +6004,10 @@
         <v>22</v>
       </c>
       <c r="P47" s="31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q47" s="26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="32">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="605" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7309FD85-4DB5-464E-BF7E-33FB67E4D7CA}"/>
+  <xr:revisionPtr revIDLastSave="607" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{834610BA-EA03-4A38-9FE8-A2424AD70DE8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="291">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2877,6 +2877,10 @@
   </si>
   <si>
     <t>TO-26</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>임시조치(프라스틱 자체가공 부착)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -5948,9 +5952,13 @@
       <c r="P46" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="Q46" s="22"/>
+      <c r="Q46" s="22" t="s">
+        <v>290</v>
+      </c>
       <c r="R46" s="22"/>
-      <c r="S46" s="36"/>
+      <c r="S46" s="36">
+        <v>46260</v>
+      </c>
       <c r="T46" s="22"/>
       <c r="U46" s="36"/>
       <c r="V46" s="15" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="607" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{834610BA-EA03-4A38-9FE8-A2424AD70DE8}"/>
+  <xr:revisionPtr revIDLastSave="624" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4EF985E-CD75-4042-B646-D8CB0BDEFB57}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="298">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2882,6 +2882,156 @@
   <si>
     <t>임시조치(프라스틱 자체가공 부착)</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 재단기(여닫이문)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-28</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연결 경첩 시공 작업</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연결 경첩 시공작업</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연결 경첩시공(목형쪽 여닫기문 부품으로 대체함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>경첩시공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>목형쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>여닫기문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부품으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대체함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3063,7 +3213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3174,6 +3324,9 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6026,28 +6179,62 @@
       <c r="V47" s="1"/>
     </row>
     <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
+      <c r="A48" s="4">
+        <v>45</v>
+      </c>
+      <c r="B48" s="7">
+        <v>46265</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46265</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="M48" s="6">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P48" s="31" t="s">
+        <v>286</v>
+      </c>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
       <c r="S48" s="32"/>
       <c r="T48" s="4"/>
       <c r="U48" s="32"/>
-      <c r="V48" s="1"/>
+      <c r="V48" s="37" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="49" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
